--- a/tests/fixtures/revenue_dummy/revenue/dummy_rev_004.xlsx
+++ b/tests/fixtures/revenue_dummy/revenue/dummy_rev_004.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ZZSHEET_ALPHA" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ZZSHEET_BETA" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ZZSHEET_GAMMA" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ZZSHEET_DELTA" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ZZSHEET_ALPHA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ZZSHEET_BETA" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ZZSHEET_GAMMA" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ZZSHEET_DELTA" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ZZSHEET_EPSILON" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -736,4 +737,2023 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O94"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ZZTITLE 1월분 거래내역</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ZZMX_CLIENT_1</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ZZMX_CLIENT_2</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ZZMX_CLIENT_3</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ZZMX_CLIENT_4</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ZZMX_CLIENT_5</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ZZMX_CLIENT_6</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="J2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>거래처
+날 짜</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ZZMX_CLIENT_1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ZZMX_CLIENT_2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ZZMX_CLIENT_3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ZZMX_CLIENT_4</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ZZMX_CLIENT_5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ZZMX_CLIENT_6</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>합   계</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="B5" t="n">
+        <v>975</v>
+      </c>
+      <c r="C5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D5" t="n">
+        <v>625</v>
+      </c>
+      <c r="F5" t="n">
+        <v>275</v>
+      </c>
+      <c r="G5" t="n">
+        <v>600</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2775</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>150</v>
+      </c>
+      <c r="C6" t="n">
+        <v>475</v>
+      </c>
+      <c r="E6" t="n">
+        <v>125</v>
+      </c>
+      <c r="F6" t="n">
+        <v>450</v>
+      </c>
+      <c r="G6" t="n">
+        <v>775</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>325</v>
+      </c>
+      <c r="D7" t="n">
+        <v>975</v>
+      </c>
+      <c r="E7" t="n">
+        <v>300</v>
+      </c>
+      <c r="F7" t="n">
+        <v>625</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>43832</v>
+      </c>
+      <c r="C8" t="n">
+        <v>825</v>
+      </c>
+      <c r="D8" t="n">
+        <v>150</v>
+      </c>
+      <c r="E8" t="n">
+        <v>475</v>
+      </c>
+      <c r="G8" t="n">
+        <v>125</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>675</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D9" t="n">
+        <v>325</v>
+      </c>
+      <c r="F9" t="n">
+        <v>975</v>
+      </c>
+      <c r="G9" t="n">
+        <v>300</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3275</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>850</v>
+      </c>
+      <c r="C10" t="n">
+        <v>175</v>
+      </c>
+      <c r="E10" t="n">
+        <v>825</v>
+      </c>
+      <c r="F10" t="n">
+        <v>150</v>
+      </c>
+      <c r="G10" t="n">
+        <v>475</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>43833</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1025</v>
+      </c>
+      <c r="D11" t="n">
+        <v>675</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F11" t="n">
+        <v>325</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="n">
+        <v>525</v>
+      </c>
+      <c r="D12" t="n">
+        <v>850</v>
+      </c>
+      <c r="E12" t="n">
+        <v>175</v>
+      </c>
+      <c r="G12" t="n">
+        <v>825</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>375</v>
+      </c>
+      <c r="C13" t="n">
+        <v>700</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1025</v>
+      </c>
+      <c r="F13" t="n">
+        <v>675</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3775</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>43834</v>
+      </c>
+      <c r="B14" t="n">
+        <v>550</v>
+      </c>
+      <c r="C14" t="n">
+        <v>875</v>
+      </c>
+      <c r="E14" t="n">
+        <v>525</v>
+      </c>
+      <c r="F14" t="n">
+        <v>850</v>
+      </c>
+      <c r="G14" t="n">
+        <v>175</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>725</v>
+      </c>
+      <c r="D15" t="n">
+        <v>375</v>
+      </c>
+      <c r="E15" t="n">
+        <v>700</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1025</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2825</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="n">
+        <v>225</v>
+      </c>
+      <c r="D16" t="n">
+        <v>550</v>
+      </c>
+      <c r="E16" t="n">
+        <v>875</v>
+      </c>
+      <c r="G16" t="n">
+        <v>525</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>43835</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1075</v>
+      </c>
+      <c r="C17" t="n">
+        <v>400</v>
+      </c>
+      <c r="D17" t="n">
+        <v>725</v>
+      </c>
+      <c r="F17" t="n">
+        <v>375</v>
+      </c>
+      <c r="G17" t="n">
+        <v>700</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3275</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>250</v>
+      </c>
+      <c r="C18" t="n">
+        <v>575</v>
+      </c>
+      <c r="E18" t="n">
+        <v>225</v>
+      </c>
+      <c r="F18" t="n">
+        <v>550</v>
+      </c>
+      <c r="G18" t="n">
+        <v>875</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>425</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1075</v>
+      </c>
+      <c r="E19" t="n">
+        <v>400</v>
+      </c>
+      <c r="F19" t="n">
+        <v>725</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>43836</v>
+      </c>
+      <c r="C20" t="n">
+        <v>925</v>
+      </c>
+      <c r="D20" t="n">
+        <v>250</v>
+      </c>
+      <c r="E20" t="n">
+        <v>575</v>
+      </c>
+      <c r="G20" t="n">
+        <v>225</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>775</v>
+      </c>
+      <c r="C21" t="n">
+        <v>100</v>
+      </c>
+      <c r="D21" t="n">
+        <v>425</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1075</v>
+      </c>
+      <c r="G21" t="n">
+        <v>400</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2775</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>950</v>
+      </c>
+      <c r="C22" t="n">
+        <v>275</v>
+      </c>
+      <c r="E22" t="n">
+        <v>925</v>
+      </c>
+      <c r="F22" t="n">
+        <v>250</v>
+      </c>
+      <c r="G22" t="n">
+        <v>575</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>43837</v>
+      </c>
+      <c r="B23" t="n">
+        <v>125</v>
+      </c>
+      <c r="D23" t="n">
+        <v>775</v>
+      </c>
+      <c r="E23" t="n">
+        <v>100</v>
+      </c>
+      <c r="F23" t="n">
+        <v>425</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="n">
+        <v>625</v>
+      </c>
+      <c r="D24" t="n">
+        <v>950</v>
+      </c>
+      <c r="E24" t="n">
+        <v>275</v>
+      </c>
+      <c r="G24" t="n">
+        <v>925</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2775</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>475</v>
+      </c>
+      <c r="C25" t="n">
+        <v>800</v>
+      </c>
+      <c r="D25" t="n">
+        <v>125</v>
+      </c>
+      <c r="F25" t="n">
+        <v>775</v>
+      </c>
+      <c r="G25" t="n">
+        <v>100</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>43838</v>
+      </c>
+      <c r="B26" t="n">
+        <v>650</v>
+      </c>
+      <c r="C26" t="n">
+        <v>975</v>
+      </c>
+      <c r="E26" t="n">
+        <v>625</v>
+      </c>
+      <c r="F26" t="n">
+        <v>950</v>
+      </c>
+      <c r="G26" t="n">
+        <v>275</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3475</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>825</v>
+      </c>
+      <c r="D27" t="n">
+        <v>475</v>
+      </c>
+      <c r="E27" t="n">
+        <v>800</v>
+      </c>
+      <c r="F27" t="n">
+        <v>125</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="n">
+        <v>325</v>
+      </c>
+      <c r="D28" t="n">
+        <v>650</v>
+      </c>
+      <c r="E28" t="n">
+        <v>975</v>
+      </c>
+      <c r="G28" t="n">
+        <v>625</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>43839</v>
+      </c>
+      <c r="B29" t="n">
+        <v>175</v>
+      </c>
+      <c r="C29" t="n">
+        <v>500</v>
+      </c>
+      <c r="D29" t="n">
+        <v>825</v>
+      </c>
+      <c r="F29" t="n">
+        <v>475</v>
+      </c>
+      <c r="G29" t="n">
+        <v>800</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2775</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>350</v>
+      </c>
+      <c r="C30" t="n">
+        <v>675</v>
+      </c>
+      <c r="E30" t="n">
+        <v>325</v>
+      </c>
+      <c r="F30" t="n">
+        <v>650</v>
+      </c>
+      <c r="G30" t="n">
+        <v>975</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>525</v>
+      </c>
+      <c r="D31" t="n">
+        <v>175</v>
+      </c>
+      <c r="E31" t="n">
+        <v>500</v>
+      </c>
+      <c r="F31" t="n">
+        <v>825</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>43840</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1025</v>
+      </c>
+      <c r="D32" t="n">
+        <v>350</v>
+      </c>
+      <c r="E32" t="n">
+        <v>675</v>
+      </c>
+      <c r="G32" t="n">
+        <v>325</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>875</v>
+      </c>
+      <c r="C33" t="n">
+        <v>200</v>
+      </c>
+      <c r="D33" t="n">
+        <v>525</v>
+      </c>
+      <c r="F33" t="n">
+        <v>175</v>
+      </c>
+      <c r="G33" t="n">
+        <v>500</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1050</v>
+      </c>
+      <c r="C34" t="n">
+        <v>375</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1025</v>
+      </c>
+      <c r="F34" t="n">
+        <v>350</v>
+      </c>
+      <c r="G34" t="n">
+        <v>675</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3475</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>43841</v>
+      </c>
+      <c r="B35" t="n">
+        <v>225</v>
+      </c>
+      <c r="D35" t="n">
+        <v>875</v>
+      </c>
+      <c r="E35" t="n">
+        <v>200</v>
+      </c>
+      <c r="F35" t="n">
+        <v>525</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="n">
+        <v>725</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E36" t="n">
+        <v>375</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1025</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3175</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>575</v>
+      </c>
+      <c r="C37" t="n">
+        <v>900</v>
+      </c>
+      <c r="D37" t="n">
+        <v>225</v>
+      </c>
+      <c r="F37" t="n">
+        <v>875</v>
+      </c>
+      <c r="G37" t="n">
+        <v>200</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2775</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>43842</v>
+      </c>
+      <c r="B38" t="n">
+        <v>750</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1075</v>
+      </c>
+      <c r="E38" t="n">
+        <v>725</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1050</v>
+      </c>
+      <c r="G38" t="n">
+        <v>375</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3975</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>925</v>
+      </c>
+      <c r="D39" t="n">
+        <v>575</v>
+      </c>
+      <c r="E39" t="n">
+        <v>900</v>
+      </c>
+      <c r="F39" t="n">
+        <v>225</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="n">
+        <v>425</v>
+      </c>
+      <c r="D40" t="n">
+        <v>750</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1075</v>
+      </c>
+      <c r="G40" t="n">
+        <v>725</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>43843</v>
+      </c>
+      <c r="B41" t="n">
+        <v>275</v>
+      </c>
+      <c r="C41" t="n">
+        <v>600</v>
+      </c>
+      <c r="D41" t="n">
+        <v>925</v>
+      </c>
+      <c r="F41" t="n">
+        <v>575</v>
+      </c>
+      <c r="G41" t="n">
+        <v>900</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3275</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>450</v>
+      </c>
+      <c r="C42" t="n">
+        <v>775</v>
+      </c>
+      <c r="E42" t="n">
+        <v>425</v>
+      </c>
+      <c r="F42" t="n">
+        <v>750</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1075</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3475</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>625</v>
+      </c>
+      <c r="D43" t="n">
+        <v>275</v>
+      </c>
+      <c r="E43" t="n">
+        <v>600</v>
+      </c>
+      <c r="F43" t="n">
+        <v>925</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>43844</v>
+      </c>
+      <c r="C44" t="n">
+        <v>125</v>
+      </c>
+      <c r="D44" t="n">
+        <v>450</v>
+      </c>
+      <c r="E44" t="n">
+        <v>775</v>
+      </c>
+      <c r="G44" t="n">
+        <v>425</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>975</v>
+      </c>
+      <c r="C45" t="n">
+        <v>300</v>
+      </c>
+      <c r="D45" t="n">
+        <v>625</v>
+      </c>
+      <c r="F45" t="n">
+        <v>275</v>
+      </c>
+      <c r="G45" t="n">
+        <v>600</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2775</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>150</v>
+      </c>
+      <c r="C46" t="n">
+        <v>475</v>
+      </c>
+      <c r="E46" t="n">
+        <v>125</v>
+      </c>
+      <c r="F46" t="n">
+        <v>450</v>
+      </c>
+      <c r="G46" t="n">
+        <v>775</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>43845</v>
+      </c>
+      <c r="B47" t="n">
+        <v>325</v>
+      </c>
+      <c r="D47" t="n">
+        <v>975</v>
+      </c>
+      <c r="E47" t="n">
+        <v>300</v>
+      </c>
+      <c r="F47" t="n">
+        <v>625</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="n">
+        <v>825</v>
+      </c>
+      <c r="D48" t="n">
+        <v>150</v>
+      </c>
+      <c r="E48" t="n">
+        <v>475</v>
+      </c>
+      <c r="G48" t="n">
+        <v>125</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>675</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D49" t="n">
+        <v>325</v>
+      </c>
+      <c r="F49" t="n">
+        <v>975</v>
+      </c>
+      <c r="G49" t="n">
+        <v>300</v>
+      </c>
+      <c r="H49" t="n">
+        <v>3275</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>43846</v>
+      </c>
+      <c r="B50" t="n">
+        <v>850</v>
+      </c>
+      <c r="C50" t="n">
+        <v>175</v>
+      </c>
+      <c r="E50" t="n">
+        <v>825</v>
+      </c>
+      <c r="F50" t="n">
+        <v>150</v>
+      </c>
+      <c r="G50" t="n">
+        <v>475</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1025</v>
+      </c>
+      <c r="D51" t="n">
+        <v>675</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F51" t="n">
+        <v>325</v>
+      </c>
+      <c r="H51" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="n">
+        <v>525</v>
+      </c>
+      <c r="D52" t="n">
+        <v>850</v>
+      </c>
+      <c r="E52" t="n">
+        <v>175</v>
+      </c>
+      <c r="G52" t="n">
+        <v>825</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2375</v>
+      </c>
+      <c r="J52" t="n">
+        <v>175</v>
+      </c>
+      <c r="K52" t="n">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>43847</v>
+      </c>
+      <c r="B53" t="n">
+        <v>375</v>
+      </c>
+      <c r="C53" t="n">
+        <v>700</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1025</v>
+      </c>
+      <c r="F53" t="n">
+        <v>675</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H53" t="n">
+        <v>3775</v>
+      </c>
+      <c r="J53" t="n">
+        <v>176</v>
+      </c>
+      <c r="K53" t="n">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>550</v>
+      </c>
+      <c r="C54" t="n">
+        <v>875</v>
+      </c>
+      <c r="E54" t="n">
+        <v>525</v>
+      </c>
+      <c r="F54" t="n">
+        <v>850</v>
+      </c>
+      <c r="G54" t="n">
+        <v>175</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2975</v>
+      </c>
+      <c r="J54" t="n">
+        <v>177</v>
+      </c>
+      <c r="K54" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>725</v>
+      </c>
+      <c r="D55" t="n">
+        <v>375</v>
+      </c>
+      <c r="E55" t="n">
+        <v>700</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1025</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2825</v>
+      </c>
+      <c r="J55" t="n">
+        <v>178</v>
+      </c>
+      <c r="K55" t="n">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>43848</v>
+      </c>
+      <c r="C56" t="n">
+        <v>225</v>
+      </c>
+      <c r="D56" t="n">
+        <v>550</v>
+      </c>
+      <c r="E56" t="n">
+        <v>875</v>
+      </c>
+      <c r="G56" t="n">
+        <v>525</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2175</v>
+      </c>
+      <c r="J56" t="n">
+        <v>179</v>
+      </c>
+      <c r="K56" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>1075</v>
+      </c>
+      <c r="C57" t="n">
+        <v>400</v>
+      </c>
+      <c r="D57" t="n">
+        <v>725</v>
+      </c>
+      <c r="F57" t="n">
+        <v>375</v>
+      </c>
+      <c r="G57" t="n">
+        <v>700</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3275</v>
+      </c>
+      <c r="J57" t="n">
+        <v>180</v>
+      </c>
+      <c r="K57" t="n">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>250</v>
+      </c>
+      <c r="C58" t="n">
+        <v>575</v>
+      </c>
+      <c r="E58" t="n">
+        <v>225</v>
+      </c>
+      <c r="F58" t="n">
+        <v>550</v>
+      </c>
+      <c r="G58" t="n">
+        <v>875</v>
+      </c>
+      <c r="H58" t="n">
+        <v>2475</v>
+      </c>
+      <c r="J58" t="n">
+        <v>181</v>
+      </c>
+      <c r="K58" t="n">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>43849</v>
+      </c>
+      <c r="B59" t="n">
+        <v>425</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1075</v>
+      </c>
+      <c r="E59" t="n">
+        <v>400</v>
+      </c>
+      <c r="F59" t="n">
+        <v>725</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2625</v>
+      </c>
+      <c r="J59" t="n">
+        <v>182</v>
+      </c>
+      <c r="K59" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="n">
+        <v>925</v>
+      </c>
+      <c r="D60" t="n">
+        <v>250</v>
+      </c>
+      <c r="E60" t="n">
+        <v>575</v>
+      </c>
+      <c r="G60" t="n">
+        <v>225</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1975</v>
+      </c>
+      <c r="J60" t="n">
+        <v>183</v>
+      </c>
+      <c r="K60" t="n">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>775</v>
+      </c>
+      <c r="C61" t="n">
+        <v>100</v>
+      </c>
+      <c r="D61" t="n">
+        <v>425</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1075</v>
+      </c>
+      <c r="G61" t="n">
+        <v>400</v>
+      </c>
+      <c r="H61" t="n">
+        <v>2775</v>
+      </c>
+      <c r="J61" t="n">
+        <v>184</v>
+      </c>
+      <c r="K61" t="n">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>43850</v>
+      </c>
+      <c r="B62" t="n">
+        <v>950</v>
+      </c>
+      <c r="C62" t="n">
+        <v>275</v>
+      </c>
+      <c r="E62" t="n">
+        <v>925</v>
+      </c>
+      <c r="F62" t="n">
+        <v>250</v>
+      </c>
+      <c r="G62" t="n">
+        <v>575</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2975</v>
+      </c>
+      <c r="J62" t="n">
+        <v>185</v>
+      </c>
+      <c r="K62" t="n">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>125</v>
+      </c>
+      <c r="D63" t="n">
+        <v>775</v>
+      </c>
+      <c r="E63" t="n">
+        <v>100</v>
+      </c>
+      <c r="F63" t="n">
+        <v>425</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1425</v>
+      </c>
+      <c r="J63" t="n">
+        <v>186</v>
+      </c>
+      <c r="K63" t="n">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" t="n">
+        <v>625</v>
+      </c>
+      <c r="D64" t="n">
+        <v>950</v>
+      </c>
+      <c r="E64" t="n">
+        <v>275</v>
+      </c>
+      <c r="G64" t="n">
+        <v>925</v>
+      </c>
+      <c r="H64" t="n">
+        <v>2775</v>
+      </c>
+      <c r="J64" t="n">
+        <v>187</v>
+      </c>
+      <c r="K64" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>43851</v>
+      </c>
+      <c r="B65" t="n">
+        <v>475</v>
+      </c>
+      <c r="C65" t="n">
+        <v>800</v>
+      </c>
+      <c r="D65" t="n">
+        <v>125</v>
+      </c>
+      <c r="F65" t="n">
+        <v>775</v>
+      </c>
+      <c r="G65" t="n">
+        <v>100</v>
+      </c>
+      <c r="H65" t="n">
+        <v>2275</v>
+      </c>
+      <c r="J65" t="n">
+        <v>188</v>
+      </c>
+      <c r="K65" t="n">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>650</v>
+      </c>
+      <c r="C66" t="n">
+        <v>975</v>
+      </c>
+      <c r="E66" t="n">
+        <v>625</v>
+      </c>
+      <c r="F66" t="n">
+        <v>950</v>
+      </c>
+      <c r="G66" t="n">
+        <v>275</v>
+      </c>
+      <c r="H66" t="n">
+        <v>3475</v>
+      </c>
+      <c r="J66" t="n">
+        <v>189</v>
+      </c>
+      <c r="K66" t="n">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>825</v>
+      </c>
+      <c r="D67" t="n">
+        <v>475</v>
+      </c>
+      <c r="E67" t="n">
+        <v>800</v>
+      </c>
+      <c r="F67" t="n">
+        <v>125</v>
+      </c>
+      <c r="H67" t="n">
+        <v>2225</v>
+      </c>
+      <c r="J67" t="n">
+        <v>190</v>
+      </c>
+      <c r="K67" t="n">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>43852</v>
+      </c>
+      <c r="C68" t="n">
+        <v>325</v>
+      </c>
+      <c r="D68" t="n">
+        <v>650</v>
+      </c>
+      <c r="E68" t="n">
+        <v>975</v>
+      </c>
+      <c r="G68" t="n">
+        <v>625</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2575</v>
+      </c>
+      <c r="J68" t="n">
+        <v>191</v>
+      </c>
+      <c r="K68" t="n">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>175</v>
+      </c>
+      <c r="C69" t="n">
+        <v>500</v>
+      </c>
+      <c r="D69" t="n">
+        <v>825</v>
+      </c>
+      <c r="F69" t="n">
+        <v>475</v>
+      </c>
+      <c r="G69" t="n">
+        <v>800</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2775</v>
+      </c>
+      <c r="J69" t="n">
+        <v>192</v>
+      </c>
+      <c r="K69" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>350</v>
+      </c>
+      <c r="C70" t="n">
+        <v>675</v>
+      </c>
+      <c r="E70" t="n">
+        <v>325</v>
+      </c>
+      <c r="F70" t="n">
+        <v>650</v>
+      </c>
+      <c r="G70" t="n">
+        <v>975</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2975</v>
+      </c>
+      <c r="J70" t="n">
+        <v>193</v>
+      </c>
+      <c r="K70" t="n">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>43853</v>
+      </c>
+      <c r="B71" t="n">
+        <v>525</v>
+      </c>
+      <c r="D71" t="n">
+        <v>175</v>
+      </c>
+      <c r="E71" t="n">
+        <v>500</v>
+      </c>
+      <c r="F71" t="n">
+        <v>825</v>
+      </c>
+      <c r="H71" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J71" t="n">
+        <v>194</v>
+      </c>
+      <c r="K71" t="n">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="C72" t="n">
+        <v>1025</v>
+      </c>
+      <c r="D72" t="n">
+        <v>350</v>
+      </c>
+      <c r="E72" t="n">
+        <v>675</v>
+      </c>
+      <c r="G72" t="n">
+        <v>325</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>875</v>
+      </c>
+      <c r="C73" t="n">
+        <v>200</v>
+      </c>
+      <c r="D73" t="n">
+        <v>525</v>
+      </c>
+      <c r="F73" t="n">
+        <v>175</v>
+      </c>
+      <c r="G73" t="n">
+        <v>500</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>43854</v>
+      </c>
+      <c r="B74" t="n">
+        <v>1050</v>
+      </c>
+      <c r="C74" t="n">
+        <v>375</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1025</v>
+      </c>
+      <c r="F74" t="n">
+        <v>350</v>
+      </c>
+      <c r="G74" t="n">
+        <v>675</v>
+      </c>
+      <c r="H74" t="n">
+        <v>3475</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>225</v>
+      </c>
+      <c r="D75" t="n">
+        <v>875</v>
+      </c>
+      <c r="E75" t="n">
+        <v>200</v>
+      </c>
+      <c r="F75" t="n">
+        <v>525</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="C76" t="n">
+        <v>725</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E76" t="n">
+        <v>375</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1025</v>
+      </c>
+      <c r="H76" t="n">
+        <v>3175</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>43855</v>
+      </c>
+      <c r="B77" t="n">
+        <v>575</v>
+      </c>
+      <c r="C77" t="n">
+        <v>900</v>
+      </c>
+      <c r="D77" t="n">
+        <v>225</v>
+      </c>
+      <c r="F77" t="n">
+        <v>875</v>
+      </c>
+      <c r="G77" t="n">
+        <v>200</v>
+      </c>
+      <c r="H77" t="n">
+        <v>2775</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>750</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1075</v>
+      </c>
+      <c r="E78" t="n">
+        <v>725</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1050</v>
+      </c>
+      <c r="G78" t="n">
+        <v>375</v>
+      </c>
+      <c r="H78" t="n">
+        <v>3975</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>925</v>
+      </c>
+      <c r="D79" t="n">
+        <v>575</v>
+      </c>
+      <c r="E79" t="n">
+        <v>900</v>
+      </c>
+      <c r="F79" t="n">
+        <v>225</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>43856</v>
+      </c>
+      <c r="C80" t="n">
+        <v>425</v>
+      </c>
+      <c r="D80" t="n">
+        <v>750</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1075</v>
+      </c>
+      <c r="G80" t="n">
+        <v>725</v>
+      </c>
+      <c r="H80" t="n">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>275</v>
+      </c>
+      <c r="C81" t="n">
+        <v>600</v>
+      </c>
+      <c r="D81" t="n">
+        <v>925</v>
+      </c>
+      <c r="F81" t="n">
+        <v>575</v>
+      </c>
+      <c r="G81" t="n">
+        <v>900</v>
+      </c>
+      <c r="H81" t="n">
+        <v>3275</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>합    계</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>34.925</v>
+      </c>
+      <c r="C82" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="D82" t="n">
+        <v>35.275</v>
+      </c>
+      <c r="E82" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="F82" t="n">
+        <v>34.325</v>
+      </c>
+      <c r="G82" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="H82" t="n">
+        <v>205.325</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>단가(회사인정)</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>마감자료제출시삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>공 급 가 액</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>34925</v>
+      </c>
+      <c r="C85" t="n">
+        <v>37510</v>
+      </c>
+      <c r="D85" t="n">
+        <v>42330</v>
+      </c>
+      <c r="E85" t="n">
+        <v>43160.00000000001</v>
+      </c>
+      <c r="F85" t="n">
+        <v>48055.00000000001</v>
+      </c>
+      <c r="G85" t="n">
+        <v>50250</v>
+      </c>
+      <c r="H85" t="n">
+        <v>256230</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>부  가  세</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>3492.5</v>
+      </c>
+      <c r="C86" t="n">
+        <v>3751</v>
+      </c>
+      <c r="D86" t="n">
+        <v>4233</v>
+      </c>
+      <c r="E86" t="n">
+        <v>4316.000000000001</v>
+      </c>
+      <c r="F86" t="n">
+        <v>4805.500000000001</v>
+      </c>
+      <c r="G86" t="n">
+        <v>5025</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>회사받은금액</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>38417.5</v>
+      </c>
+      <c r="C87" t="n">
+        <v>41261</v>
+      </c>
+      <c r="D87" t="n">
+        <v>46563.00000000001</v>
+      </c>
+      <c r="E87" t="n">
+        <v>47476.00000000001</v>
+      </c>
+      <c r="F87" t="n">
+        <v>52860.50000000001</v>
+      </c>
+      <c r="G87" t="n">
+        <v>55275.00000000001</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>단가(발행단가)</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>공 급 가 액</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>41910</v>
+      </c>
+      <c r="C90" t="n">
+        <v>44330</v>
+      </c>
+      <c r="D90" t="n">
+        <v>49385</v>
+      </c>
+      <c r="E90" t="n">
+        <v>49800.00000000001</v>
+      </c>
+      <c r="F90" t="n">
+        <v>54920.00000000001</v>
+      </c>
+      <c r="G90" t="n">
+        <v>56950</v>
+      </c>
+      <c r="H90" t="n">
+        <v>297295</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>부  가  세</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>4191</v>
+      </c>
+      <c r="C91" t="n">
+        <v>4433</v>
+      </c>
+      <c r="D91" t="n">
+        <v>4938.5</v>
+      </c>
+      <c r="E91" t="n">
+        <v>4980.000000000001</v>
+      </c>
+      <c r="F91" t="n">
+        <v>5492.000000000001</v>
+      </c>
+      <c r="G91" t="n">
+        <v>5695</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>청구한 금액</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>46101.00000000001</v>
+      </c>
+      <c r="C92" t="n">
+        <v>48763.00000000001</v>
+      </c>
+      <c r="D92" t="n">
+        <v>54323.50000000001</v>
+      </c>
+      <c r="E92" t="n">
+        <v>54780.00000000001</v>
+      </c>
+      <c r="F92" t="n">
+        <v>60412.00000000001</v>
+      </c>
+      <c r="G92" t="n">
+        <v>62645.00000000001</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>차이 금액</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>7683.5</v>
+      </c>
+      <c r="C94" t="n">
+        <v>7502.000000000001</v>
+      </c>
+      <c r="D94" t="n">
+        <v>7760.500000000001</v>
+      </c>
+      <c r="E94" t="n">
+        <v>7304.000000000002</v>
+      </c>
+      <c r="F94" t="n">
+        <v>7551.500000000002</v>
+      </c>
+      <c r="G94" t="n">
+        <v>7370.000000000001</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>제출시삭제</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="D3:D4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>